--- a/exports/students.xlsx
+++ b/exports/students.xlsx
@@ -421,107 +421,107 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>rakesh</v>
+        <v>Jane Smith</v>
       </c>
       <c r="B2">
-        <v>984589246</v>
+        <v>8765432109</v>
       </c>
       <c r="C2" t="str">
-        <v>sahanirakesh877@gmail.com</v>
+        <v>jane@example.com</v>
       </c>
       <c r="D2" t="str">
-        <v>1</v>
+        <v>R102</v>
       </c>
       <c r="E2" t="str">
-        <v>class 12</v>
+        <v>B</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Jane Smith</v>
+        <v>Robert Brown</v>
       </c>
       <c r="B3">
-        <v>8765432109</v>
+        <v>7654321098</v>
       </c>
       <c r="C3" t="str">
-        <v>jane@example.com</v>
+        <v>robert@example.com</v>
       </c>
       <c r="D3" t="str">
-        <v>R102</v>
+        <v>R103</v>
       </c>
       <c r="E3" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Robert Brown</v>
+        <v>Emily Davis</v>
       </c>
       <c r="B4">
-        <v>7654321098</v>
+        <v>6543210987</v>
       </c>
       <c r="C4" t="str">
-        <v>robert@example.com</v>
+        <v>emily@example.com</v>
       </c>
       <c r="D4" t="str">
-        <v>R103</v>
+        <v>R104</v>
       </c>
       <c r="E4" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Emily Davis</v>
+        <v>Michael Wilson</v>
       </c>
       <c r="B5">
-        <v>6543210987</v>
+        <v>5432109876</v>
       </c>
       <c r="C5" t="str">
-        <v>emily@example.com</v>
+        <v>michael@example.com</v>
       </c>
       <c r="D5" t="str">
-        <v>R104</v>
+        <v>R105</v>
       </c>
       <c r="E5" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Michael Wilson</v>
+        <v xml:space="preserve"> rolex</v>
       </c>
       <c r="B6">
-        <v>5432109876</v>
+        <v>984589246</v>
       </c>
       <c r="C6" t="str">
-        <v>michael@example.com</v>
+        <v>sahanirakesh877@gmail.com</v>
       </c>
       <c r="D6" t="str">
-        <v>R105</v>
+        <v>10</v>
       </c>
       <c r="E6" t="str">
-        <v>B</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v xml:space="preserve"> ranzeth</v>
+        <v xml:space="preserve"> shristy</v>
       </c>
       <c r="B7">
         <v>984589246</v>
@@ -530,7 +530,7 @@
         <v>sahanirakesh877@gmail.com</v>
       </c>
       <c r="D7" t="str">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E7" t="str">
         <v>2</v>
@@ -541,7 +541,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v xml:space="preserve"> rolex</v>
+        <v xml:space="preserve"> sudhira Ray</v>
       </c>
       <c r="B8">
         <v>984589246</v>
@@ -550,7 +550,7 @@
         <v>sahanirakesh877@gmail.com</v>
       </c>
       <c r="D8" t="str">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E8" t="str">
         <v>2</v>
@@ -561,7 +561,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v xml:space="preserve"> sahani</v>
+        <v xml:space="preserve"> glowin</v>
       </c>
       <c r="B9">
         <v>984589246</v>
@@ -570,7 +570,7 @@
         <v>sahanirakesh877@gmail.com</v>
       </c>
       <c r="D9" t="str">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E9" t="str">
         <v>2</v>
@@ -581,7 +581,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v xml:space="preserve"> lumi</v>
+        <v xml:space="preserve"> angel</v>
       </c>
       <c r="B10">
         <v>984589246</v>
@@ -590,7 +590,7 @@
         <v>sahanirakesh877@gmail.com</v>
       </c>
       <c r="D10" t="str">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E10" t="str">
         <v>2</v>
@@ -601,47 +601,47 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v xml:space="preserve"> shrisry</v>
+        <v>bibek</v>
       </c>
       <c r="B11">
-        <v>984589246</v>
+        <v>1234567890</v>
       </c>
       <c r="C11" t="str">
-        <v>sahanirakesh877@gmail.com</v>
+        <v>bibek@gmail.com</v>
       </c>
       <c r="D11" t="str">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E11" t="str">
-        <v>2</v>
+        <v>5B</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v xml:space="preserve"> sudhira</v>
+        <v>nitesh</v>
       </c>
       <c r="B12">
-        <v>984589246</v>
+        <v>987654321</v>
       </c>
       <c r="C12" t="str">
-        <v>sahanirakesh877@gmail.com</v>
+        <v>nitesh@example.com</v>
       </c>
       <c r="D12" t="str">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E12" t="str">
-        <v>2</v>
+        <v>12B</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v xml:space="preserve"> glowin</v>
+        <v xml:space="preserve"> hello </v>
       </c>
       <c r="B13">
         <v>984589246</v>
@@ -650,7 +650,7 @@
         <v>sahanirakesh877@gmail.com</v>
       </c>
       <c r="D13" t="str">
-        <v>16</v>
+        <v>171</v>
       </c>
       <c r="E13" t="str">
         <v>2</v>
@@ -661,62 +661,62 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v xml:space="preserve"> angel</v>
+        <v>Rakesh Kumar Sahani</v>
       </c>
       <c r="B14">
-        <v>984589246</v>
+        <v>9845892346</v>
       </c>
       <c r="C14" t="str">
-        <v>sahanirakesh877@gmail.com</v>
+        <v>admin@example.com</v>
       </c>
       <c r="D14" t="str">
-        <v>17</v>
+        <v>221</v>
       </c>
       <c r="E14" t="str">
-        <v>2</v>
+        <v>c</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>bibek</v>
+        <v>Football</v>
       </c>
       <c r="B15">
-        <v>1234567890</v>
+        <v>9845892346</v>
       </c>
       <c r="C15" t="str">
-        <v>bibek@gmail.com</v>
+        <v>thunderbolts@admin.com</v>
       </c>
       <c r="D15" t="str">
-        <v>25</v>
+        <v>444</v>
       </c>
       <c r="E15" t="str">
-        <v>5B</v>
+        <v>class 11</v>
       </c>
       <c r="F15">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>nitesh</v>
+        <v>Rizan Maharjan</v>
       </c>
       <c r="B16">
-        <v>987654321</v>
+        <v>1234567890</v>
       </c>
       <c r="C16" t="str">
-        <v>nitesh@example.com</v>
+        <v>rijan@123gmail.com</v>
       </c>
       <c r="D16" t="str">
-        <v>26</v>
+        <v>342</v>
       </c>
       <c r="E16" t="str">
-        <v>12B</v>
+        <v>class 10</v>
       </c>
       <c r="F16">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
